--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -6126,11 +6126,14 @@
       <c r="C335" t="str">
         <v>Psicologia</v>
       </c>
-      <c r="D335" t="b">
-        <v>0</v>
+      <c r="D335" t="str">
+        <v>publicado</v>
       </c>
       <c r="E335" t="str">
-        <v/>
+        <v>13/09/2026</v>
+      </c>
+      <c r="F335" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=1JMjv5CYH94 | Short: https://www.youtube.com/watch?v=j887yqbCjS4</v>
       </c>
     </row>
     <row r="336">

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -17739,11 +17739,14 @@
       <c r="C1013" t="str">
         <v>Países e Culturas</v>
       </c>
-      <c r="D1013" t="b">
-        <v>0</v>
+      <c r="D1013" t="str">
+        <v>publicado</v>
       </c>
       <c r="E1013" t="str">
-        <v/>
+        <v>14/09/2026</v>
+      </c>
+      <c r="F1013" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=iohsPbTOlYA | Short: https://www.youtube.com/watch?v=hpv_DiRt7Mc</v>
       </c>
     </row>
     <row r="1014">

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -15511,11 +15511,14 @@
       <c r="C883" t="str">
         <v>Profissões e Processos</v>
       </c>
-      <c r="D883" t="b">
-        <v>0</v>
+      <c r="D883" t="str">
+        <v>publicado</v>
       </c>
       <c r="E883" t="str">
-        <v/>
+        <v>15/09/2026</v>
+      </c>
+      <c r="F883" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=qmpEccEYkog | Short: https://www.youtube.com/watch?v=eExlLzebnZc</v>
       </c>
     </row>
     <row r="884">

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -8731,11 +8731,14 @@
       <c r="C487" t="str">
         <v>Música e Arte</v>
       </c>
-      <c r="D487" t="b">
-        <v>0</v>
+      <c r="D487" t="str">
+        <v>publicado</v>
       </c>
       <c r="E487" t="str">
-        <v/>
+        <v>16/09/2026</v>
+      </c>
+      <c r="F487" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=gs5__8Kc258 | Short: https://www.youtube.com/watch?v=DlomNLcTo0c</v>
       </c>
     </row>
     <row r="488">

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -7155,11 +7155,14 @@
       <c r="C395" t="str">
         <v>Alimentação</v>
       </c>
-      <c r="D395" t="b">
-        <v>0</v>
+      <c r="D395" t="str">
+        <v>publicado</v>
       </c>
       <c r="E395" t="str">
-        <v/>
+        <v>17/09/2026</v>
+      </c>
+      <c r="F395" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=CIknUoBIg8M | Short: https://www.youtube.com/watch?v=4tlbI1ZD_R4</v>
       </c>
     </row>
     <row r="396">

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -17425,11 +17425,14 @@
       <c r="C994" t="str">
         <v>Profissões e Processos</v>
       </c>
-      <c r="D994" t="b">
-        <v>0</v>
+      <c r="D994" t="str">
+        <v>publicado</v>
       </c>
       <c r="E994" t="str">
-        <v/>
+        <v>18/09/2026</v>
+      </c>
+      <c r="F994" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=O6tV9noh-xs | Short: https://www.youtube.com/watch?v=PwwJR7tKH1U</v>
       </c>
     </row>
     <row r="995">

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -22879,11 +22879,14 @@
       <c r="C1312" t="str">
         <v>Máquinas e Mecânica</v>
       </c>
-      <c r="D1312" t="b">
-        <v>0</v>
+      <c r="D1312" t="str">
+        <v>publicado</v>
       </c>
       <c r="E1312" t="str">
-        <v/>
+        <v>19/09/2026</v>
+      </c>
+      <c r="F1312" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=Kw9i6HrmXc4 | Short: https://www.youtube.com/watch?v=lN6Gi0HiL3E</v>
       </c>
     </row>
     <row r="1313">

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -12748,11 +12748,14 @@
       <c r="C721" t="str">
         <v>Tecnologia e Cotidiano</v>
       </c>
-      <c r="D721" t="b">
-        <v>0</v>
+      <c r="D721" t="str">
+        <v>publicado</v>
       </c>
       <c r="E721" t="str">
-        <v/>
+        <v>20/09/2026</v>
+      </c>
+      <c r="F721" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=j9A0ukLloQ8 | Short: https://www.youtube.com/watch?v=Ph8XbMvC7HM</v>
       </c>
     </row>
     <row r="722">

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -8771,11 +8771,14 @@
       <c r="C489" t="str">
         <v>Corpo Humano</v>
       </c>
-      <c r="D489" t="b">
-        <v>0</v>
+      <c r="D489" t="str">
+        <v>publicado</v>
       </c>
       <c r="E489" t="str">
-        <v/>
+        <v>21/09/2026</v>
+      </c>
+      <c r="F489" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=R2nomHTpb8o | Short: https://www.youtube.com/watch?v=nZoTbqq4a80</v>
       </c>
     </row>
     <row r="490">

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -1568,11 +1568,14 @@
       <c r="C69" t="str">
         <v>Saúde</v>
       </c>
-      <c r="D69" t="b">
-        <v>0</v>
+      <c r="D69" t="str">
+        <v>publicado</v>
       </c>
       <c r="E69" t="str">
-        <v/>
+        <v>22/09/2026</v>
+      </c>
+      <c r="F69" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=FK-s7PSh83w | Short: https://www.youtube.com/watch?v=_Sp7e6DP9lo</v>
       </c>
     </row>
     <row r="70">

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -14432,11 +14432,14 @@
       <c r="C819" t="str">
         <v>Comparações e Diferenças</v>
       </c>
-      <c r="D819" t="b">
-        <v>0</v>
+      <c r="D819" t="str">
+        <v>publicado</v>
       </c>
       <c r="E819" t="str">
-        <v/>
+        <v>23/09/2026</v>
+      </c>
+      <c r="F819" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=MwF6kmTR4ws | Short: https://www.youtube.com/watch?v=VsTI1DDm01s</v>
       </c>
     </row>
     <row r="820">

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -21131,11 +21131,14 @@
       <c r="C1209" t="str">
         <v>Animais Específicos</v>
       </c>
-      <c r="D1209" t="b">
-        <v>0</v>
+      <c r="D1209" t="str">
+        <v>publicado</v>
       </c>
       <c r="E1209" t="str">
-        <v/>
+        <v>24/09/2026</v>
+      </c>
+      <c r="F1209" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=xlS8Rc-prsQ | Short: https://www.youtube.com/watch?v=6Jd-KpxPNQQ</v>
       </c>
     </row>
     <row r="1210">

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -3068,11 +3068,14 @@
       <c r="C156" t="str">
         <v>Curiosidades</v>
       </c>
-      <c r="D156" t="b">
-        <v>0</v>
+      <c r="D156" t="str">
+        <v>publicado</v>
       </c>
       <c r="E156" t="str">
-        <v/>
+        <v>25/09/2026</v>
+      </c>
+      <c r="F156" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=siIt_3rVl3w | Short: https://www.youtube.com/watch?v=_kJKgl9_N8s</v>
       </c>
     </row>
     <row r="157">

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -13908,11 +13908,14 @@
       <c r="C788" t="str">
         <v>Comparações e Diferenças</v>
       </c>
-      <c r="D788" t="b">
-        <v>0</v>
+      <c r="D788" t="str">
+        <v>publicado</v>
       </c>
       <c r="E788" t="str">
-        <v/>
+        <v>26/09/2026</v>
+      </c>
+      <c r="F788" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=vqPsX7XzEHw | Short: https://www.youtube.com/watch?v=kAo_WSDVY40</v>
       </c>
     </row>
     <row r="789">

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -23578,11 +23578,14 @@
       <c r="C1351" t="str">
         <v>Máquinas e Mecânica</v>
       </c>
-      <c r="D1351" t="b">
-        <v>0</v>
+      <c r="D1351" t="str">
+        <v>publicado</v>
       </c>
       <c r="E1351" t="str">
-        <v/>
+        <v>27/09/2026</v>
+      </c>
+      <c r="F1351" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=zVsr0YBwz18 | Short: https://www.youtube.com/watch?v=GlN_qMujT5c</v>
       </c>
     </row>
     <row r="1352">

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -19827,11 +19827,14 @@
       <c r="C1133" t="str">
         <v>Países e Culturas</v>
       </c>
-      <c r="D1133" t="b">
-        <v>0</v>
+      <c r="D1133" t="str">
+        <v>publicado</v>
       </c>
       <c r="E1133" t="str">
-        <v/>
+        <v>28/09/2026</v>
+      </c>
+      <c r="F1133" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=Gjuq_7BW2mk | Short: https://www.youtube.com/watch?v=OFnayJXEyzc</v>
       </c>
     </row>
     <row r="1134">

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -9140,11 +9140,14 @@
       <c r="C510" t="str">
         <v>Corpo Humano</v>
       </c>
-      <c r="D510" t="b">
-        <v>0</v>
+      <c r="D510" t="str">
+        <v>publicado</v>
       </c>
       <c r="E510" t="str">
-        <v/>
+        <v>29/09/2026</v>
+      </c>
+      <c r="F510" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=5xWPqkmgxag | Short: https://www.youtube.com/watch?v=BBklSzAZYR0</v>
       </c>
     </row>
     <row r="511">

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -2229,11 +2229,14 @@
       <c r="C107" t="str">
         <v>Tecnologia</v>
       </c>
-      <c r="D107" t="b">
-        <v>0</v>
+      <c r="D107" t="str">
+        <v>publicado</v>
       </c>
       <c r="E107" t="str">
-        <v/>
+        <v>30/09/2026</v>
+      </c>
+      <c r="F107" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=iYoX48EM_VE | Short: https://www.youtube.com/watch?v=IaDQ5UVkORk</v>
       </c>
     </row>
     <row r="108">

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -8936,11 +8936,14 @@
       <c r="C498" t="str">
         <v>Corpo Humano</v>
       </c>
-      <c r="D498" t="b">
-        <v>0</v>
+      <c r="D498" t="str">
+        <v>publicado</v>
       </c>
       <c r="E498" t="str">
-        <v/>
+        <v>01/10/2026</v>
+      </c>
+      <c r="F498" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=XqfR15OEBqA | Short: https://www.youtube.com/watch?v=PKdle9Fv2zs</v>
       </c>
     </row>
     <row r="499">

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -5302,11 +5302,14 @@
       <c r="C286" t="str">
         <v>Animais</v>
       </c>
-      <c r="D286" t="b">
-        <v>0</v>
+      <c r="D286" t="str">
+        <v>publicado</v>
       </c>
       <c r="E286" t="str">
-        <v/>
+        <v>02/10/2026</v>
+      </c>
+      <c r="F286" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=E8YcLkqhnlc | Short: https://www.youtube.com/watch?v=aIhqutY7Clo</v>
       </c>
     </row>
     <row r="287">

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -15601,11 +15601,14 @@
       <c r="C886" t="str">
         <v>Profissões e Processos</v>
       </c>
-      <c r="D886" t="b">
-        <v>0</v>
+      <c r="D886" t="str">
+        <v>publicado</v>
       </c>
       <c r="E886" t="str">
-        <v/>
+        <v>03/10/2026</v>
+      </c>
+      <c r="F886" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=hyXwEywhiek | Short: https://www.youtube.com/watch?v=3izoCBnf9wI</v>
       </c>
     </row>
     <row r="887">
